--- a/docs/検証工種候補一覧_260608.xlsx
+++ b/docs/検証工種候補一覧_260608.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\imoo\Desktop\ClaudeCode\14.歩掛Jsonからテストケース作成可能か【進行中】\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDDEC40E-6BB4-4949-8AF9-4399E4940451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96FEBBD2-3167-4A93-8213-F4872D050E3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="284">
   <si>
     <t>推奨度</t>
   </si>
@@ -841,6 +841,58 @@
   </si>
   <si>
     <t>題名</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>#9</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>#10</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>#11</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>#12</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>#13</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>#14</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>#15</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>#16</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>#17</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>#18</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>#19</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>#20</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>#21</t>
     <phoneticPr fontId="5"/>
   </si>
 </sst>
@@ -892,7 +944,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -924,8 +976,14 @@
         <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -948,11 +1006,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -981,6 +1050,22 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1284,7 +1369,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:M60"/>
+  <dimension ref="A1:N60"/>
   <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="2" width="8" customWidth="1"/>
@@ -1301,7 +1386,7 @@
     <col min="13" max="13" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="30" customHeight="1">
+    <row r="1" spans="1:14" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1342,7 +1427,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="30" hidden="1">
+    <row r="2" spans="1:14" ht="30" hidden="1">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -1379,7 +1464,7 @@
       </c>
       <c r="M2" s="3"/>
     </row>
-    <row r="3" spans="1:13" ht="30" hidden="1">
+    <row r="3" spans="1:14" ht="30" hidden="1">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -1416,7 +1501,7 @@
       </c>
       <c r="M3" s="3"/>
     </row>
-    <row r="4" spans="1:13" ht="30" hidden="1">
+    <row r="4" spans="1:14" ht="30" hidden="1">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -1453,7 +1538,7 @@
       </c>
       <c r="M4" s="3"/>
     </row>
-    <row r="5" spans="1:13" ht="30">
+    <row r="5" spans="1:14" ht="30">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -1493,8 +1578,11 @@
       <c r="M5" s="3" t="s">
         <v>267</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="30" hidden="1">
+      <c r="N5" s="10" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="30" hidden="1">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -1531,7 +1619,7 @@
       </c>
       <c r="M6" s="3"/>
     </row>
-    <row r="7" spans="1:13" ht="30" hidden="1">
+    <row r="7" spans="1:14" ht="30" hidden="1">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -1568,7 +1656,7 @@
       </c>
       <c r="M7" s="3"/>
     </row>
-    <row r="8" spans="1:13" ht="30" hidden="1">
+    <row r="8" spans="1:14" ht="30" hidden="1">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -1605,7 +1693,7 @@
       </c>
       <c r="M8" s="3"/>
     </row>
-    <row r="9" spans="1:13" ht="30">
+    <row r="9" spans="1:14" ht="30">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
@@ -1643,8 +1731,11 @@
       <c r="M9" s="3" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" ht="30" hidden="1">
+      <c r="N9" s="10" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="30" hidden="1">
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
@@ -1681,7 +1772,7 @@
       </c>
       <c r="M10" s="3"/>
     </row>
-    <row r="11" spans="1:13" ht="30" hidden="1">
+    <row r="11" spans="1:14" ht="30" hidden="1">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -1718,7 +1809,7 @@
       </c>
       <c r="M11" s="3"/>
     </row>
-    <row r="12" spans="1:13" ht="30" hidden="1">
+    <row r="12" spans="1:14" ht="30" hidden="1">
       <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
@@ -1755,7 +1846,7 @@
       </c>
       <c r="M12" s="3"/>
     </row>
-    <row r="13" spans="1:13" ht="30" hidden="1">
+    <row r="13" spans="1:14" ht="30" hidden="1">
       <c r="A13" s="2" t="s">
         <v>10</v>
       </c>
@@ -1792,7 +1883,7 @@
       </c>
       <c r="M13" s="3"/>
     </row>
-    <row r="14" spans="1:13" ht="30" hidden="1">
+    <row r="14" spans="1:14" ht="30" hidden="1">
       <c r="A14" s="2" t="s">
         <v>10</v>
       </c>
@@ -1829,48 +1920,51 @@
       </c>
       <c r="M14" s="3"/>
     </row>
-    <row r="15" spans="1:13" ht="17.399999999999999">
-      <c r="A15" s="2" t="s">
+    <row r="15" spans="1:14" s="15" customFormat="1" ht="17.399999999999999">
+      <c r="A15" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="E15" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="F15" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="G15" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="H15" s="4" t="s">
+      <c r="H15" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="I15" s="3" t="s">
+      <c r="I15" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K15" s="3" t="s">
+      <c r="J15" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="K15" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="L15" s="4" t="s">
+      <c r="L15" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="M15" s="3" t="s">
+      <c r="M15" s="11" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" ht="45">
+      <c r="N15" s="14" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="45">
       <c r="A16" s="6" t="s">
         <v>72</v>
       </c>
@@ -1910,8 +2004,11 @@
       <c r="M16" s="3" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="17" spans="1:13" ht="30" hidden="1">
+      <c r="N16" s="10" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="30" hidden="1">
       <c r="A17" s="6" t="s">
         <v>72</v>
       </c>
@@ -1948,7 +2045,7 @@
       </c>
       <c r="M17" s="3"/>
     </row>
-    <row r="18" spans="1:13" ht="30" hidden="1">
+    <row r="18" spans="1:14" ht="30" hidden="1">
       <c r="A18" s="6" t="s">
         <v>72</v>
       </c>
@@ -1985,7 +2082,7 @@
       </c>
       <c r="M18" s="3"/>
     </row>
-    <row r="19" spans="1:13" ht="30" hidden="1">
+    <row r="19" spans="1:14" ht="30" hidden="1">
       <c r="A19" s="6" t="s">
         <v>72</v>
       </c>
@@ -2022,7 +2119,7 @@
       </c>
       <c r="M19" s="3"/>
     </row>
-    <row r="20" spans="1:13" ht="30" hidden="1">
+    <row r="20" spans="1:14" ht="30" hidden="1">
       <c r="A20" s="6" t="s">
         <v>72</v>
       </c>
@@ -2059,7 +2156,7 @@
       </c>
       <c r="M20" s="3"/>
     </row>
-    <row r="21" spans="1:13" ht="30" hidden="1">
+    <row r="21" spans="1:14" ht="30" hidden="1">
       <c r="A21" s="6" t="s">
         <v>72</v>
       </c>
@@ -2096,87 +2193,93 @@
       </c>
       <c r="M21" s="3"/>
     </row>
-    <row r="22" spans="1:13" ht="30">
-      <c r="A22" s="6" t="s">
+    <row r="22" spans="1:14" s="15" customFormat="1" ht="30">
+      <c r="A22" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="E22" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F22" s="3" t="s">
+      <c r="F22" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="G22" s="3" t="s">
+      <c r="G22" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="H22" s="4" t="s">
+      <c r="H22" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="I22" s="3" t="s">
+      <c r="I22" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K22" s="3" t="s">
+      <c r="J22" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="K22" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="L22" s="4" t="s">
+      <c r="L22" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="M22" s="3" t="s">
+      <c r="M22" s="11" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="23" spans="1:13" ht="30">
-      <c r="A23" s="6" t="s">
+      <c r="N22" s="14" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" s="15" customFormat="1" ht="30">
+      <c r="A23" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3" t="s">
+      <c r="B23" s="11"/>
+      <c r="C23" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="E23" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F23" s="3" t="s">
+      <c r="F23" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="G23" s="3" t="s">
+      <c r="G23" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="H23" s="4" t="s">
+      <c r="H23" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="I23" s="3" t="s">
+      <c r="I23" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="J23" s="3" t="s">
+      <c r="J23" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="K23" s="3" t="s">
+      <c r="K23" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="L23" s="4" t="s">
+      <c r="L23" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="M23" s="3" t="s">
+      <c r="M23" s="11" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="24" spans="1:13" ht="30" hidden="1">
+      <c r="N23" s="14" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="30" hidden="1">
       <c r="A24" s="6" t="s">
         <v>72</v>
       </c>
@@ -2213,7 +2316,7 @@
       </c>
       <c r="M24" s="3"/>
     </row>
-    <row r="25" spans="1:13" ht="30">
+    <row r="25" spans="1:14" ht="30">
       <c r="A25" s="6" t="s">
         <v>72</v>
       </c>
@@ -2253,8 +2356,11 @@
       <c r="M25" s="3" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="26" spans="1:13" ht="15" hidden="1">
+      <c r="N25" s="10" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="15" hidden="1">
       <c r="A26" s="6" t="s">
         <v>72</v>
       </c>
@@ -2291,7 +2397,7 @@
       </c>
       <c r="M26" s="3"/>
     </row>
-    <row r="27" spans="1:13" ht="15" hidden="1">
+    <row r="27" spans="1:14" ht="15" hidden="1">
       <c r="A27" s="6" t="s">
         <v>72</v>
       </c>
@@ -2328,7 +2434,7 @@
       </c>
       <c r="M27" s="3"/>
     </row>
-    <row r="28" spans="1:13" ht="30">
+    <row r="28" spans="1:14" ht="30">
       <c r="A28" s="6" t="s">
         <v>72</v>
       </c>
@@ -2366,8 +2472,11 @@
       <c r="M28" s="3" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="29" spans="1:13" ht="30" hidden="1">
+      <c r="N28" s="10" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="30" hidden="1">
       <c r="A29" s="6" t="s">
         <v>72</v>
       </c>
@@ -2404,7 +2513,7 @@
       </c>
       <c r="M29" s="3"/>
     </row>
-    <row r="30" spans="1:13" ht="30" hidden="1">
+    <row r="30" spans="1:14" ht="30" hidden="1">
       <c r="A30" s="6" t="s">
         <v>72</v>
       </c>
@@ -2441,7 +2550,7 @@
       </c>
       <c r="M30" s="3"/>
     </row>
-    <row r="31" spans="1:13" ht="30">
+    <row r="31" spans="1:14" ht="30">
       <c r="A31" s="6" t="s">
         <v>72</v>
       </c>
@@ -2479,8 +2588,11 @@
       <c r="M31" s="3" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="32" spans="1:13" ht="30" hidden="1">
+      <c r="N31" s="10" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="30" hidden="1">
       <c r="A32" s="6" t="s">
         <v>72</v>
       </c>
@@ -2517,7 +2629,7 @@
       </c>
       <c r="M32" s="3"/>
     </row>
-    <row r="33" spans="1:13" ht="30" hidden="1">
+    <row r="33" spans="1:14" ht="30" hidden="1">
       <c r="A33" s="6" t="s">
         <v>72</v>
       </c>
@@ -2554,7 +2666,7 @@
       </c>
       <c r="M33" s="3"/>
     </row>
-    <row r="34" spans="1:13" ht="30" hidden="1">
+    <row r="34" spans="1:14" ht="30" hidden="1">
       <c r="A34" s="6" t="s">
         <v>72</v>
       </c>
@@ -2591,7 +2703,7 @@
       </c>
       <c r="M34" s="3"/>
     </row>
-    <row r="35" spans="1:13" ht="30" hidden="1">
+    <row r="35" spans="1:14" ht="30" hidden="1">
       <c r="A35" s="6" t="s">
         <v>72</v>
       </c>
@@ -2628,7 +2740,7 @@
       </c>
       <c r="M35" s="3"/>
     </row>
-    <row r="36" spans="1:13" ht="30">
+    <row r="36" spans="1:14" ht="30">
       <c r="A36" s="6" t="s">
         <v>72</v>
       </c>
@@ -2666,8 +2778,11 @@
       <c r="M36" s="3" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="37" spans="1:13" ht="30" hidden="1">
+      <c r="N36" s="10" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" ht="30" hidden="1">
       <c r="A37" s="6" t="s">
         <v>72</v>
       </c>
@@ -2704,7 +2819,7 @@
       </c>
       <c r="M37" s="3"/>
     </row>
-    <row r="38" spans="1:13" ht="30" hidden="1">
+    <row r="38" spans="1:14" ht="30" hidden="1">
       <c r="A38" s="6" t="s">
         <v>72</v>
       </c>
@@ -2741,7 +2856,7 @@
       </c>
       <c r="M38" s="3"/>
     </row>
-    <row r="39" spans="1:13" ht="30" hidden="1">
+    <row r="39" spans="1:14" ht="30" hidden="1">
       <c r="A39" s="6" t="s">
         <v>72</v>
       </c>
@@ -2778,7 +2893,7 @@
       </c>
       <c r="M39" s="3"/>
     </row>
-    <row r="40" spans="1:13" ht="30" hidden="1">
+    <row r="40" spans="1:14" ht="30" hidden="1">
       <c r="A40" s="6" t="s">
         <v>72</v>
       </c>
@@ -2815,7 +2930,7 @@
       </c>
       <c r="M40" s="3"/>
     </row>
-    <row r="41" spans="1:13" ht="30">
+    <row r="41" spans="1:14" ht="30">
       <c r="A41" s="6" t="s">
         <v>72</v>
       </c>
@@ -2853,8 +2968,11 @@
       <c r="M41" s="3" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="42" spans="1:13" ht="45" hidden="1">
+      <c r="N41" s="10" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" ht="45" hidden="1">
       <c r="A42" s="6" t="s">
         <v>72</v>
       </c>
@@ -2891,7 +3009,7 @@
       </c>
       <c r="M42" s="3"/>
     </row>
-    <row r="43" spans="1:13" ht="30" hidden="1">
+    <row r="43" spans="1:14" ht="30" hidden="1">
       <c r="A43" s="6" t="s">
         <v>72</v>
       </c>
@@ -2928,7 +3046,7 @@
       </c>
       <c r="M43" s="3"/>
     </row>
-    <row r="44" spans="1:13" ht="30" hidden="1">
+    <row r="44" spans="1:14" ht="30" hidden="1">
       <c r="A44" s="6" t="s">
         <v>72</v>
       </c>
@@ -2965,7 +3083,7 @@
       </c>
       <c r="M44" s="3"/>
     </row>
-    <row r="45" spans="1:13" ht="60" hidden="1">
+    <row r="45" spans="1:14" ht="60" hidden="1">
       <c r="A45" s="6" t="s">
         <v>72</v>
       </c>
@@ -3002,7 +3120,7 @@
       </c>
       <c r="M45" s="3"/>
     </row>
-    <row r="46" spans="1:13" ht="30">
+    <row r="46" spans="1:14" ht="30">
       <c r="A46" s="6" t="s">
         <v>72</v>
       </c>
@@ -3040,8 +3158,11 @@
       <c r="M46" s="3" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="47" spans="1:13" ht="30" hidden="1">
+      <c r="N46" s="10" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" ht="30" hidden="1">
       <c r="A47" s="6" t="s">
         <v>72</v>
       </c>
@@ -3078,7 +3199,7 @@
       </c>
       <c r="M47" s="3"/>
     </row>
-    <row r="48" spans="1:13" ht="30" hidden="1">
+    <row r="48" spans="1:14" ht="30" hidden="1">
       <c r="A48" s="6" t="s">
         <v>72</v>
       </c>
@@ -3115,7 +3236,7 @@
       </c>
       <c r="M48" s="3"/>
     </row>
-    <row r="49" spans="1:13" ht="30" hidden="1">
+    <row r="49" spans="1:14" ht="30" hidden="1">
       <c r="A49" s="6" t="s">
         <v>72</v>
       </c>
@@ -3152,7 +3273,7 @@
       </c>
       <c r="M49" s="3"/>
     </row>
-    <row r="50" spans="1:13" ht="30" hidden="1">
+    <row r="50" spans="1:14" ht="30" hidden="1">
       <c r="A50" s="6" t="s">
         <v>72</v>
       </c>
@@ -3189,7 +3310,7 @@
       </c>
       <c r="M50" s="3"/>
     </row>
-    <row r="51" spans="1:13" ht="30">
+    <row r="51" spans="1:14" ht="30">
       <c r="A51" s="6" t="s">
         <v>72</v>
       </c>
@@ -3227,8 +3348,11 @@
       <c r="M51" s="3" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="52" spans="1:13" ht="30" hidden="1">
+      <c r="N51" s="10" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" ht="30" hidden="1">
       <c r="A52" s="6" t="s">
         <v>72</v>
       </c>
@@ -3265,7 +3389,7 @@
       </c>
       <c r="M52" s="3"/>
     </row>
-    <row r="53" spans="1:13" ht="30" hidden="1">
+    <row r="53" spans="1:14" ht="30" hidden="1">
       <c r="A53" s="7" t="s">
         <v>212</v>
       </c>
@@ -3302,7 +3426,7 @@
       </c>
       <c r="M53" s="3"/>
     </row>
-    <row r="54" spans="1:13" ht="30" hidden="1">
+    <row r="54" spans="1:14" ht="30" hidden="1">
       <c r="A54" s="7" t="s">
         <v>212</v>
       </c>
@@ -3339,7 +3463,7 @@
       </c>
       <c r="M54" s="3"/>
     </row>
-    <row r="55" spans="1:13" ht="30" hidden="1">
+    <row r="55" spans="1:14" ht="30" hidden="1">
       <c r="A55" s="7" t="s">
         <v>212</v>
       </c>
@@ -3376,7 +3500,7 @@
       </c>
       <c r="M55" s="3"/>
     </row>
-    <row r="56" spans="1:13" ht="30" hidden="1">
+    <row r="56" spans="1:14" ht="30" hidden="1">
       <c r="A56" s="7" t="s">
         <v>212</v>
       </c>
@@ -3413,7 +3537,7 @@
       </c>
       <c r="M56" s="3"/>
     </row>
-    <row r="57" spans="1:13" ht="30" hidden="1">
+    <row r="57" spans="1:14" ht="30" hidden="1">
       <c r="A57" s="7" t="s">
         <v>212</v>
       </c>
@@ -3450,7 +3574,7 @@
       </c>
       <c r="M57" s="3"/>
     </row>
-    <row r="58" spans="1:13" ht="30" hidden="1">
+    <row r="58" spans="1:14" ht="30" hidden="1">
       <c r="A58" s="7" t="s">
         <v>212</v>
       </c>
@@ -3487,7 +3611,7 @@
       </c>
       <c r="M58" s="3"/>
     </row>
-    <row r="59" spans="1:13" ht="30" hidden="1">
+    <row r="59" spans="1:14" ht="30" hidden="1">
       <c r="A59" s="7" t="s">
         <v>212</v>
       </c>
@@ -3524,7 +3648,7 @@
       </c>
       <c r="M59" s="3"/>
     </row>
-    <row r="60" spans="1:13" ht="30" hidden="1">
+    <row r="60" spans="1:14" ht="30" hidden="1">
       <c r="A60" s="7" t="s">
         <v>212</v>
       </c>
